--- a/gte/nodes/LPC/compressor_stage_2_blade_rotor_coordinates_lattice.xlsx
+++ b/gte/nodes/LPC/compressor_stage_2_blade_rotor_coordinates_lattice.xlsx
@@ -346,10 +346,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>-21.91426080468235</v>
+        <v>-21.847297134569</v>
       </c>
       <c r="B1">
-        <v>21.158209775848096</v>
+        <v>21.218597568179781</v>
       </c>
       <c r="C1">
         <v>374.58109848544609</v>
@@ -357,10 +357,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>-19.361173086180358</v>
+        <v>-19.298525276071423</v>
       </c>
       <c r="B2">
-        <v>20.94826354155564</v>
+        <v>21.001114571123253</v>
       </c>
       <c r="C2">
         <v>374.58109848544609</v>
@@ -368,10 +368,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>-17.46353514853919</v>
+        <v>-17.405769554804564</v>
       </c>
       <c r="B3">
-        <v>20.268126129996336</v>
+        <v>20.314874251175809</v>
       </c>
       <c r="C3">
         <v>374.58109848544609</v>
@@ -379,10 +379,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>-15.68665074544284</v>
+        <v>-15.633643755545945</v>
       </c>
       <c r="B4">
-        <v>19.501365382485659</v>
+        <v>19.542437638039871</v>
       </c>
       <c r="C4">
         <v>374.58109848544609</v>
@@ -390,10 +390,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>-14.000001840542961</v>
+        <v>-13.951607295217986</v>
       </c>
       <c r="B5">
-        <v>18.669873611535571</v>
+        <v>18.705627551537233</v>
       </c>
       <c r="C5">
         <v>374.58109848544609</v>
@@ -401,10 +401,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>-12.390720361512218</v>
+        <v>-12.346790995485565</v>
       </c>
       <c r="B6">
-        <v>17.782881812797331</v>
+        <v>17.813639682508121</v>
       </c>
       <c r="C6">
         <v>374.58109848544609</v>
@@ -412,10 +412,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>-10.85122018587694</v>
+        <v>-10.811612405446171</v>
       </c>
       <c r="B7">
-        <v>16.845831940728683</v>
+        <v>16.871892082711174</v>
       </c>
       <c r="C7">
         <v>374.58109848544609</v>
@@ -423,10 +423,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>-9.3768016194550565</v>
+        <v>-9.34137834165357</v>
       </c>
       <c r="B8">
-        <v>15.862095351617773</v>
+        <v>15.883738273474959</v>
       </c>
       <c r="C8">
         <v>374.58109848544609</v>
@@ -434,10 +434,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>-7.9605643396981911</v>
+        <v>-7.9291900562737263</v>
       </c>
       <c r="B9">
-        <v>14.836622036870917</v>
+        <v>14.854107765496636</v>
       </c>
       <c r="C9">
         <v>374.58109848544609</v>
@@ -445,10 +445,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-6.5951415783593088</v>
+        <v>-6.5676808533839859</v>
       </c>
       <c r="B10">
-        <v>13.774696595760057</v>
+        <v>13.788264442487705</v>
       </c>
       <c r="C10">
         <v>374.58109848544609</v>
@@ -456,10 +456,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-5.273501412763018</v>
+        <v>-5.2498178090950693</v>
       </c>
       <c r="B11">
-        <v>12.681363423901358</v>
+        <v>12.691233690848497</v>
       </c>
       <c r="C11">
         <v>374.58109848544609</v>
@@ -467,10 +467,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-3.9917155790027987</v>
+        <v>-3.9716750877625482</v>
       </c>
       <c r="B12">
-        <v>11.559440487041014</v>
+        <v>11.565820722375408</v>
       </c>
       <c r="C12">
         <v>374.58109848544609</v>
@@ -478,10 +478,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-2.7579356026759672</v>
+        <v>-2.7414214346881089</v>
       </c>
       <c r="B13">
-        <v>10.403080235101152</v>
+        <v>10.406188547760291</v>
       </c>
       <c r="C13">
         <v>374.58109848544609</v>
@@ -489,10 +489,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-1.5769259562650175</v>
+        <v>-1.5638334458640495</v>
       </c>
       <c r="B14">
-        <v>9.2088648426571282</v>
+        <v>9.2089240431136385</v>
       </c>
       <c r="C14">
         <v>374.58109848544609</v>
@@ -500,10 +500,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-0.42782311028937564</v>
+        <v>-0.4180245390990982</v>
       </c>
       <c r="B15">
-        <v>7.9917608987213447</v>
+        <v>7.9889517473250748</v>
       </c>
       <c r="C15">
         <v>374.58109848544609</v>
@@ -511,10 +511,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>0.708506198056427</v>
+        <v>0.71515976442732387</v>
       </c>
       <c r="B16">
-        <v>6.7654937742164174</v>
+        <v>6.7599585222014</v>
       </c>
       <c r="C16">
         <v>374.58109848544609</v>
@@ -522,10 +522,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>1.8186461629143926</v>
+        <v>1.8222823518694171</v>
       </c>
       <c r="B17">
-        <v>5.5204395532687629</v>
+        <v>5.5123428584389291</v>
       </c>
       <c r="C17">
         <v>374.58109848544609</v>
@@ -533,10 +533,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>2.885185222101172</v>
+        <v>2.885905569302496</v>
       </c>
       <c r="B18">
-        <v>4.2441079381315587</v>
+        <v>4.2336446540564321</v>
       </c>
       <c r="C18">
         <v>374.58109848544609</v>
@@ -544,10 +544,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>3.9072778567955284</v>
+        <v>3.905181190152736</v>
       </c>
       <c r="B19">
-        <v>2.9358923903611926</v>
+        <v>2.923257807472897</v>
       </c>
       <c r="C19">
         <v>374.58109848544609</v>
@@ -555,10 +555,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>4.88822005901676</v>
+        <v>4.8834083446840477</v>
       </c>
       <c r="B20">
-        <v>1.5981573113398233</v>
+        <v>1.5835397172073515</v>
       </c>
       <c r="C20">
         <v>374.58109848544609</v>
@@ -566,10 +566,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>5.8313078207841507</v>
+        <v>5.8238861631603145</v>
       </c>
       <c r="B21">
-        <v>0.23326710244963611</v>
+        <v>0.21684778177884395</v>
       </c>
       <c r="C21">
         <v>374.58109848544609</v>
@@ -577,10 +577,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>6.7392396456759851</v>
+        <v>6.7293158979257806</v>
       </c>
       <c r="B22">
-        <v>-1.156842447159123</v>
+        <v>-1.1748878148652109</v>
       </c>
       <c r="C22">
         <v>374.58109848544609</v>
@@ -588,10 +588,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>7.6123240835064641</v>
+        <v>7.600007289646</v>
       </c>
       <c r="B23">
-        <v>-2.5719499972638675</v>
+        <v>-2.5914457470638381</v>
       </c>
       <c r="C23">
         <v>374.58109848544609</v>
@@ -599,10 +599,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>8.45027219564877</v>
+        <v>8.43567220106687</v>
       </c>
       <c r="B24">
-        <v>-4.0122628198739285</v>
+        <v>-4.0330319037276734</v>
       </c>
       <c r="C24">
         <v>374.58109848544609</v>
@@ -610,10 +610,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>9.2527950434760982</v>
+        <v>9.2360224949342964</v>
       </c>
       <c r="B25">
-        <v>-5.4779881869986573</v>
+        <v>-5.49985217376737</v>
       </c>
       <c r="C25">
         <v>374.58109848544609</v>
@@ -621,10 +621,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>10.019485117564566</v>
+        <v>10.000651727361847</v>
       </c>
       <c r="B26">
-        <v>-6.9694184281823528</v>
+        <v>-6.992196982276587</v>
       </c>
       <c r="C26">
         <v>374.58109848544609</v>
@@ -632,10 +632,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>10.749460625302032</v>
+        <v>10.72868022793382</v>
       </c>
       <c r="B27">
-        <v>-8.487186103109261</v>
+        <v>-8.5106948990811286</v>
       </c>
       <c r="C27">
         <v>374.58109848544609</v>
@@ -643,10 +643,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>11.441721203279281</v>
+        <v>11.419110019602185</v>
       </c>
       <c r="B28">
-        <v>-10.032008828998578</v>
+        <v>-10.056059030189795</v>
       </c>
       <c r="C28">
         <v>374.58109848544609</v>
@@ -654,10 +654,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>12.095266488087106</v>
+        <v>12.070943125318916</v>
       </c>
       <c r="B29">
-        <v>-11.60460422306952</v>
+        <v>-11.629002481611419</v>
       </c>
       <c r="C29">
         <v>374.58109848544609</v>
@@ -665,10 +665,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>12.709495764228095</v>
+        <v>12.683582274189305</v>
       </c>
       <c r="B30">
-        <v>-13.20540321250396</v>
+        <v>-13.229952034167</v>
       </c>
       <c r="C30">
         <v>374.58109848544609</v>
@@ -676,10 +676,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>13.285406907852035</v>
+        <v>13.258033019931897</v>
       </c>
       <c r="B31">
-        <v>-14.833689964334456</v>
+        <v>-14.858189167926334</v>
       </c>
       <c r="C31">
         <v>374.58109848544609</v>
@@ -687,10 +687,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>13.824397443020535</v>
+        <v>13.795701622418582</v>
       </c>
       <c r="B32">
-        <v>-16.488461955556261</v>
+        <v>-16.512709037771437</v>
       </c>
       <c r="C32">
         <v>374.58109848544609</v>
@@ -698,10 +698,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>14.327864893795182</v>
+        <v>14.297994341521228</v>
       </c>
       <c r="B33">
-        <v>-18.168716663164613</v>
+        <v>-18.19250679858429</v>
       </c>
       <c r="C33">
         <v>374.58109848544609</v>
@@ -709,10 +709,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>14.796479074591948</v>
+        <v>14.765589565449318</v>
       </c>
       <c r="B34">
-        <v>-19.8739735914175</v>
+        <v>-19.89709770704394</v>
       </c>
       <c r="C34">
         <v>374.58109848544609</v>
@@ -720,10 +720,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>15.227998961244342</v>
+        <v>15.196254195762803</v>
       </c>
       <c r="B35">
-        <v>-21.605840353623975</v>
+        <v>-21.628077427017644</v>
       </c>
       <c r="C35">
         <v>374.58109848544609</v>
@@ -731,10 +731,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>15.619455819940246</v>
+        <v>15.587027262359239</v>
       </c>
       <c r="B36">
-        <v>-23.366446590355853</v>
+        <v>-23.387561724169675</v>
       </c>
       <c r="C36">
         <v>374.58109848544609</v>
@@ -742,10 +742,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>15.967880916867552</v>
+        <v>15.934947795136198</v>
       </c>
       <c r="B37">
-        <v>-25.157921942184974</v>
+        <v>-25.17766636416437</v>
       </c>
       <c r="C37">
         <v>374.58109848544609</v>
@@ -753,10 +753,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>16.268567554349584</v>
+        <v>16.23531564482581</v>
       </c>
       <c r="B38">
-        <v>-26.983642789402008</v>
+        <v>-27.001749845768664</v>
       </c>
       <c r="C38">
         <v>374.58109848544609</v>
@@ -764,10 +764,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>16.509857179251423</v>
+        <v>16.4764739454985</v>
       </c>
       <c r="B39">
-        <v>-28.851972471173127</v>
+        <v>-28.868141600160143</v>
       </c>
       <c r="C39">
         <v>374.58109848544609</v>
@@ -775,10 +775,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>16.678353274573595</v>
+        <v>16.645026652059254</v>
       </c>
       <c r="B40">
-        <v>-30.77252106638338</v>
+        <v>-30.78641379161904</v>
       </c>
       <c r="C40">
         <v>374.58109848544609</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>16.760659323316638</v>
+        <v>16.727577719413073</v>
       </c>
       <c r="B41">
-        <v>-32.754898653917806</v>
+        <v>-32.7661385844256</v>
       </c>
       <c r="C41">
         <v>374.58109848544609</v>
@@ -797,10 +797,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>16.760659323316638</v>
+        <v>16.727577719413073</v>
       </c>
       <c r="B42">
-        <v>-32.754898653917806</v>
+        <v>-32.7661385844256</v>
       </c>
       <c r="C42">
         <v>374.58109848544609</v>
@@ -808,10 +808,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>16.086808203218339</v>
+        <v>16.052695667451133</v>
       </c>
       <c r="B43">
-        <v>-31.196869783292918</v>
+        <v>-31.209664792398293</v>
       </c>
       <c r="C43">
         <v>374.58109848544609</v>
@@ -819,10 +819,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>15.428360224150321</v>
+        <v>15.39354013827724</v>
       </c>
       <c r="B44">
-        <v>-29.627791368940787</v>
+        <v>-29.641953589731024</v>
       </c>
       <c r="C44">
         <v>374.58109848544609</v>
@@ -830,10 +830,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>14.773675329472903</v>
+        <v>14.738437340328108</v>
       </c>
       <c r="B45">
-        <v>-28.056013481446026</v>
+        <v>-28.071346501838512</v>
       </c>
       <c r="C45">
         <v>374.58109848544609</v>
@@ -841,10 +841,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>14.111113462546413</v>
+        <v>14.07571348204047</v>
       </c>
       <c r="B46">
-        <v>-26.489886191393257</v>
+        <v>-26.506185054135511</v>
       </c>
       <c r="C46">
         <v>374.58109848544609</v>
@@ -852,10 +852,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>13.430683356945906</v>
+        <v>13.395346846328907</v>
       </c>
       <c r="B47">
-        <v>-24.936576798947822</v>
+        <v>-24.953630279720322</v>
       </c>
       <c r="C47">
         <v>374.58109848544609</v>
@@ -863,10 +863,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>12.728988907105318</v>
+        <v>12.693924014019485</v>
       </c>
       <c r="B48">
-        <v>-23.398521522597946</v>
+        <v>-23.416121242425493</v>
       </c>
       <c r="C48">
         <v>374.58109848544609</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>12.004282797673303</v>
+        <v>11.969683640416115</v>
       </c>
       <c r="B49">
-        <v>-21.876973810412544</v>
+        <v>-21.894916513767107</v>
       </c>
       <c r="C49">
         <v>374.58109848544609</v>
@@ -885,10 +885,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>11.254817713298525</v>
+        <v>11.220864380822722</v>
       </c>
       <c r="B50">
-        <v>-20.373187110460556</v>
+        <v>-20.391274665261271</v>
       </c>
       <c r="C50">
         <v>374.58109848544609</v>
@@ -896,10 +896,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>10.479499141519421</v>
+        <v>10.446359365533626</v>
       </c>
       <c r="B51">
-        <v>-18.887946578398232</v>
+        <v>-18.905986612329993</v>
       </c>
       <c r="C51">
         <v>374.58109848544609</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>9.6798437814335685</v>
+        <v>9.6476796248047378</v>
       </c>
       <c r="B52">
-        <v>-17.420164200231113</v>
+        <v>-17.437972646018927</v>
       </c>
       <c r="C52">
         <v>374.58109848544609</v>
@@ -918,10 +918,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>8.8580211350283182</v>
+        <v>8.8269906638823663</v>
       </c>
       <c r="B53">
-        <v>-15.968283669552067</v>
+        <v>-15.985685401279655</v>
       </c>
       <c r="C53">
         <v>374.58109848544609</v>
@@ -929,10 +929,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>8.0162007042910179</v>
+        <v>7.9864579880127957</v>
       </c>
       <c r="B54">
-        <v>-14.530748679953923</v>
+        <v>-14.547577513063702</v>
       </c>
       <c r="C54">
         <v>374.58109848544609</v>
@@ -940,10 +940,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>7.1560961054716339</v>
+        <v>7.1277911383040253</v>
       </c>
       <c r="B55">
-        <v>-13.106329957638021</v>
+        <v>-13.122427426187185</v>
       </c>
       <c r="C55">
         <v>374.58109848544609</v>
@@ -951,10 +951,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>6.2775974118705982</v>
+        <v>6.2508757993108146</v>
       </c>
       <c r="B56">
-        <v>-11.695106359239606</v>
+        <v>-11.710316824924382</v>
       </c>
       <c r="C56">
         <v>374.58109848544609</v>
@@ -962,10 +962,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>5.3801388110509363</v>
+        <v>5.3551416914496</v>
       </c>
       <c r="B57">
-        <v>-10.297483774002384</v>
+        <v>-10.311653203414092</v>
       </c>
       <c r="C57">
         <v>374.58109848544609</v>
@@ -973,10 +973,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>4.4631544905756968</v>
+        <v>4.4400185351368346</v>
       </c>
       <c r="B58">
-        <v>-8.9138680911700874</v>
+        <v>-8.9268440557951365</v>
       </c>
       <c r="C58">
         <v>374.58109848544609</v>
@@ -984,10 +984,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>3.5261484261699141</v>
+        <v>3.5050063533651103</v>
       </c>
       <c r="B59">
-        <v>-7.5446151369930137</v>
+        <v>-7.5562466413942131</v>
       </c>
       <c r="C59">
         <v>374.58109848544609</v>
@@ -995,10 +995,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>2.5689037462066704</v>
+        <v>2.5498863794316677</v>
       </c>
       <c r="B60">
-        <v>-6.1898804857478931</v>
+        <v>-6.2000172802896092</v>
       </c>
       <c r="C60">
         <v>374.58109848544609</v>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>1.591273367221036</v>
+        <v>1.5745101492098912</v>
       </c>
       <c r="B61">
-        <v>-4.8497696487180306</v>
+        <v>-4.8582620577474964</v>
       </c>
       <c r="C61">
         <v>374.58109848544609</v>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>0.593110205748095</v>
+        <v>0.57872919857317506</v>
       </c>
       <c r="B62">
-        <v>-3.524388137186746</v>
+        <v>-3.5310870590340553</v>
       </c>
       <c r="C62">
         <v>374.58109848544609</v>
@@ -1028,10 +1028,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-0.42518364582936607</v>
+        <v>-0.4370546268040828</v>
       </c>
       <c r="B63">
-        <v>-2.2134475075595077</v>
+        <v>-2.2182051447149798</v>
       </c>
       <c r="C63">
         <v>374.58109848544609</v>
@@ -1039,10 +1039,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-1.4610093917377665</v>
+        <v>-1.4702382420434899</v>
       </c>
       <c r="B64">
-        <v>-0.9150834967303566</v>
+        <v>-0.91775627655399172</v>
       </c>
       <c r="C64">
         <v>374.58109848544609</v>
@@ -1050,10 +1050,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-2.5112190603558049</v>
+        <v>-2.5176682524656346</v>
       </c>
       <c r="B65">
-        <v>0.37296211328449647</v>
+        <v>0.37251280838565287</v>
       </c>
       <c r="C65">
         <v>374.58109848544609</v>
@@ -1061,10 +1061,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-3.5726646800621973</v>
+        <v>-3.576191263391121</v>
       </c>
       <c r="B66">
-        <v>1.6529475404688636</v>
+        <v>1.6548553730407214</v>
       </c>
       <c r="C66">
         <v>374.58109848544609</v>
@@ -1072,10 +1072,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-4.6463799402632731</v>
+        <v>-4.6468407531467681</v>
       </c>
       <c r="B67">
-        <v>2.9241312609820351</v>
+        <v>2.9285329439099432</v>
       </c>
       <c r="C67">
         <v>374.58109848544609</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-5.7501251744758664</v>
+        <v>-5.7473976920843013</v>
       </c>
       <c r="B68">
-        <v>4.1737727836852843</v>
+        <v>4.180840101739963</v>
       </c>
       <c r="C68">
         <v>374.58109848544609</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-6.897724847773401</v>
+        <v>-6.8917014290903031</v>
       </c>
       <c r="B69">
-        <v>5.3919550383502708</v>
+        <v>5.4018879188559135</v>
       </c>
       <c r="C69">
         <v>374.58109848544609</v>
@@ -1105,10 +1105,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-8.0705333073451</v>
+        <v>-8.0610773351658427</v>
       </c>
       <c r="B70">
-        <v>6.5920536056881325</v>
+        <v>6.6050203796488969</v>
       </c>
       <c r="C70">
         <v>374.58109848544609</v>
@@ -1116,10 +1116,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-9.2482244733858572</v>
+        <v>-9.2351676596436434</v>
       </c>
       <c r="B71">
-        <v>7.7886495316795887</v>
+        <v>7.8047841456433664</v>
       </c>
       <c r="C71">
         <v>374.58109848544609</v>
@@ -1127,10 +1127,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>-10.4362206759974</v>
+        <v>-10.41939614306856</v>
       </c>
       <c r="B72">
-        <v>8.9778530724441747</v>
+        <v>8.9973036748311728</v>
       </c>
       <c r="C72">
         <v>374.58109848544609</v>
@@ -1138,10 +1138,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>-11.643392758453201</v>
+        <v>-11.622639024539669</v>
       </c>
       <c r="B73">
-        <v>10.153300670675282</v>
+        <v>10.176236437141347</v>
       </c>
       <c r="C73">
         <v>374.58109848544609</v>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>-12.866657206806892</v>
+        <v>-12.841801046160818</v>
       </c>
       <c r="B74">
-        <v>11.317204305223008</v>
+        <v>11.343794153784266</v>
       </c>
       <c r="C74">
         <v>374.58109848544609</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>-14.099893920185997</v>
+        <v>-14.070745634795733</v>
       </c>
       <c r="B75">
-        <v>12.473954270383342</v>
+        <v>12.504361722374224</v>
       </c>
       <c r="C75">
         <v>374.58109848544609</v>
@@ -1171,10 +1171,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>-15.336790807233463</v>
+        <v>-15.303142453342938</v>
       </c>
       <c r="B76">
-        <v>13.628078586079168</v>
+        <v>13.662462494859863</v>
       </c>
       <c r="C76">
         <v>374.58109848544609</v>
@@ -1182,10 +1182,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>-16.571581683773683</v>
+        <v>-16.533206914481354</v>
       </c>
       <c r="B77">
-        <v>14.783713662154593</v>
+        <v>14.822229856858964</v>
       </c>
       <c r="C77">
         <v>374.58109848544609</v>
@@ -1193,10 +1193,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>-17.800875984841458</v>
+        <v>-17.757531193976668</v>
       </c>
       <c r="B78">
-        <v>15.943291742511644</v>
+        <v>15.986098874331496</v>
       </c>
       <c r="C78">
         <v>374.58109848544609</v>
@@ -1204,10 +1204,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>-19.018480846402372</v>
+        <v>-18.969900449776958</v>
       </c>
       <c r="B79">
-        <v>17.111255318575321</v>
+        <v>17.158510372063777</v>
       </c>
       <c r="C79">
         <v>374.58109848544609</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>-20.213103678457252</v>
+        <v>-20.158991098587439</v>
       </c>
       <c r="B80">
-        <v>18.29570520346839</v>
+        <v>18.347555633622722</v>
       </c>
       <c r="C80">
         <v>374.58109848544609</v>
@@ -1226,10 +1226,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>-21.355958098081697</v>
+        <v>-21.295960513717819</v>
       </c>
       <c r="B81">
-        <v>19.517291496819677</v>
+        <v>19.573844201525919</v>
       </c>
       <c r="C81">
         <v>374.58109848544609</v>
@@ -1237,10 +1237,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>-21.91426080468235</v>
+        <v>-21.847297134569</v>
       </c>
       <c r="B82">
-        <v>21.158209775848096</v>
+        <v>21.218597568179781</v>
       </c>
       <c r="C82">
         <v>374.58109848544609</v>
@@ -1258,10 +1258,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>-30.779711131219795</v>
+        <v>-30.849288672567305</v>
       </c>
       <c r="B1">
-        <v>16.359220402764507</v>
+        <v>16.235617128153471</v>
       </c>
       <c r="C1">
         <v>442.41419819725974</v>
@@ -1269,10 +1269,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>-28.689565142447126</v>
+        <v>-28.754621763058154</v>
       </c>
       <c r="B2">
-        <v>16.078980615638532</v>
+        <v>15.966744180647805</v>
       </c>
       <c r="C2">
         <v>442.41419819725974</v>
@@ -1280,10 +1280,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>-26.793612652420826</v>
+        <v>-26.853588423764233</v>
       </c>
       <c r="B3">
-        <v>15.4844102353621</v>
+        <v>15.382725184892991</v>
       </c>
       <c r="C3">
         <v>442.41419819725974</v>
@@ -1291,10 +1291,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>-24.93152688732296</v>
+        <v>-24.986495214685885</v>
       </c>
       <c r="B4">
-        <v>14.835021605228993</v>
+        <v>14.743467327908633</v>
       </c>
       <c r="C4">
         <v>442.41419819725974</v>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>-23.094377452007869</v>
+        <v>-23.144445194953338</v>
       </c>
       <c r="B5">
-        <v>14.145269876525575</v>
+        <v>14.063450721554988</v>
       </c>
       <c r="C5">
         <v>442.41419819725974</v>
@@ -1313,10 +1313,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>-21.278512840589418</v>
+        <v>-21.323799511278228</v>
       </c>
       <c r="B6">
-        <v>13.421065545836379</v>
+        <v>13.348597738862249</v>
       </c>
       <c r="C6">
         <v>442.41419819725974</v>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>-19.481842391870597</v>
+        <v>-19.522474120544</v>
       </c>
       <c r="B7">
-        <v>12.665792654225456</v>
+        <v>12.60230023978443</v>
       </c>
       <c r="C7">
         <v>442.41419819725974</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>-17.703130631026703</v>
+        <v>-17.73923685155269</v>
       </c>
       <c r="B8">
-        <v>11.881450998477897</v>
+        <v>11.826563630116473</v>
       </c>
       <c r="C8">
         <v>442.41419819725974</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>-15.940456914618986</v>
+        <v>-15.972173243144642</v>
       </c>
       <c r="B9">
-        <v>11.071149421038099</v>
+        <v>11.024503768685547</v>
       </c>
       <c r="C9">
         <v>442.41419819725974</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-14.191749564200189</v>
+        <v>-14.219218476329536</v>
       </c>
       <c r="B10">
-        <v>10.238241236612003</v>
+        <v>10.199481227444263</v>
       </c>
       <c r="C10">
         <v>442.41419819725974</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-12.455017929902928</v>
+        <v>-12.478388590756051</v>
       </c>
       <c r="B11">
-        <v>9.38594860329248</v>
+        <v>9.3547249778148061</v>
       </c>
       <c r="C11">
         <v>442.41419819725974</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-10.729194368483183</v>
+        <v>-10.748619048707226</v>
       </c>
       <c r="B12">
-        <v>8.5159996578932322</v>
+        <v>8.4919675956844074</v>
       </c>
       <c r="C12">
         <v>442.41419819725974</v>
@@ -1390,10 +1390,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-9.01682223461051</v>
+        <v>-9.03244214436454</v>
       </c>
       <c r="B13">
-        <v>7.6242776087243636</v>
+        <v>7.6070876753308632</v>
       </c>
       <c r="C13">
         <v>442.41419819725974</v>
@@ -1401,10 +1401,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-7.3194193664866818</v>
+        <v>-7.3313687942599088</v>
       </c>
       <c r="B14">
-        <v>6.70832561255811</v>
+        <v>6.6976261422572234</v>
       </c>
       <c r="C14">
         <v>442.41419819725974</v>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-5.6307905385287915</v>
+        <v>-5.6392275724286014</v>
       </c>
       <c r="B15">
-        <v>5.778171548518884</v>
+        <v>5.773627228477</v>
       </c>
       <c r="C15">
         <v>442.41419819725974</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-3.945253533856877</v>
+        <v>-3.9503580926658421</v>
       </c>
       <c r="B16">
-        <v>4.8430129160792275</v>
+        <v>4.8443034292306608</v>
       </c>
       <c r="C16">
         <v>442.41419819725974</v>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-2.2668912341873746</v>
+        <v>-2.2688264703032535</v>
       </c>
       <c r="B17">
-        <v>3.8962409737520134</v>
+        <v>3.9030369861560268</v>
       </c>
       <c r="C17">
         <v>442.41419819725974</v>
@@ -1445,10 +1445,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-0.60097868193705506</v>
+        <v>-0.59988633975439865</v>
       </c>
       <c r="B18">
-        <v>2.9293172935133516</v>
+        <v>2.9412774081242272</v>
       </c>
       <c r="C18">
         <v>442.41419819725974</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>1.0522055362724578</v>
+        <v>1.0561850897758967</v>
       </c>
       <c r="B19">
-        <v>1.9417909421518556</v>
+        <v>1.958573526542216</v>
       </c>
       <c r="C19">
         <v>442.41419819725974</v>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>2.6936319477683259</v>
+        <v>2.7003547153849858</v>
       </c>
       <c r="B20">
-        <v>0.93523286015927554</v>
+        <v>0.95649900345090844</v>
       </c>
       <c r="C20">
         <v>442.41419819725974</v>
@@ -1478,10 +1478,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>4.3242710798777066</v>
+        <v>4.3335894341702215</v>
       </c>
       <c r="B21">
-        <v>-0.088786011972642909</v>
+        <v>-0.063372499108783509</v>
       </c>
       <c r="C21">
         <v>442.41419819725974</v>
@@ -1489,10 +1489,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>5.94492033476616</v>
+        <v>5.9566836335249755</v>
       </c>
       <c r="B22">
-        <v>-1.128974962158801</v>
+        <v>-1.0997480852432249</v>
       </c>
       <c r="C22">
         <v>442.41419819725974</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>7.5556846139528391</v>
+        <v>7.5697416620267211</v>
       </c>
       <c r="B23">
-        <v>-2.1851641919407117</v>
+        <v>-2.1524579236479022</v>
       </c>
       <c r="C23">
         <v>442.41419819725974</v>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>9.1564956937952786</v>
+        <v>9.1726953585489284</v>
       </c>
       <c r="B24">
-        <v>-3.2574641312665262</v>
+        <v>-3.2216129491655723</v>
       </c>
       <c r="C24">
         <v>442.41419819725974</v>
@@ -1522,10 +1522,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>10.747285350651028</v>
+        <v>10.765476561965089</v>
       </c>
       <c r="B25">
-        <v>-4.3459852100844056</v>
+        <v>-4.3073240966390021</v>
       </c>
       <c r="C25">
         <v>442.41419819725974</v>
@@ -1533,10 +1533,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>12.327956171988598</v>
+        <v>12.347987969235051</v>
       </c>
       <c r="B26">
-        <v>-5.4508851048304869</v>
+        <v>-5.4097497304910007</v>
       </c>
       <c r="C26">
         <v>442.41419819725974</v>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>13.898293989720365</v>
+        <v>13.920015709664165</v>
       </c>
       <c r="B27">
-        <v>-6.5725104778928349</v>
+        <v>-6.5292379334645956</v>
       </c>
       <c r="C27">
         <v>442.41419819725974</v>
@@ -1555,10 +1555,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>15.458055446869643</v>
+        <v>15.481316770644115</v>
       </c>
       <c r="B28">
-        <v>-7.71125523814747</v>
+        <v>-7.6661842178828454</v>
       </c>
       <c r="C28">
         <v>442.41419819725974</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>17.006997186459774</v>
+        <v>17.031648139566617</v>
       </c>
       <c r="B29">
-        <v>-8.8675132944704362</v>
+        <v>-8.8209840960688233</v>
       </c>
       <c r="C29">
         <v>442.41419819725974</v>
@@ -1577,10 +1577,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>18.545003399963775</v>
+        <v>18.57089377548424</v>
       </c>
       <c r="B30">
-        <v>-10.041472099908354</v>
+        <v>-9.993826429106754</v>
       </c>
       <c r="C30">
         <v>442.41419819725974</v>
@@ -1588,10 +1588,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>20.072468472653448</v>
+        <v>20.099445524093085</v>
       </c>
       <c r="B31">
-        <v>-11.232493284190245</v>
+        <v>-11.184073473125503</v>
       </c>
       <c r="C31">
         <v>442.41419819725974</v>
@@ -1599,10 +1599,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>21.589914338250313</v>
+        <v>21.617822202750144</v>
       </c>
       <c r="B32">
-        <v>-12.43973202121572</v>
+        <v>-12.390880833015116</v>
       </c>
       <c r="C32">
         <v>442.41419819725974</v>
@@ -1610,10 +1610,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>23.09786293047588</v>
+        <v>23.126542628812395</v>
       </c>
       <c r="B33">
-        <v>-13.662343484884405</v>
+        <v>-13.613404113665622</v>
       </c>
       <c r="C33">
         <v>442.41419819725974</v>
@@ -1621,10 +1621,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>24.59662788856237</v>
+        <v>24.625918072603355</v>
       </c>
       <c r="B34">
-        <v>-14.899820004205555</v>
+        <v>-14.85113671070935</v>
       </c>
       <c r="C34">
         <v>442.41419819725974</v>
@@ -1632,10 +1632,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>26.085689673784891</v>
+        <v>26.115429616312749</v>
       </c>
       <c r="B35">
-        <v>-16.153002528627084</v>
+        <v>-16.104923182747868</v>
       </c>
       <c r="C35">
         <v>442.41419819725974</v>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>27.564320452929291</v>
+        <v>27.594350795096844</v>
       </c>
       <c r="B36">
-        <v>-17.423069162706554</v>
+        <v>-17.375945879125048</v>
       </c>
       <c r="C36">
         <v>442.41419819725974</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>29.031792392781405</v>
+        <v>29.0619551441119</v>
       </c>
       <c r="B37">
-        <v>-18.711198011001525</v>
+        <v>-18.665387149184749</v>
       </c>
       <c r="C37">
         <v>442.41419819725974</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>30.486868165794412</v>
+        <v>30.517008648903758</v>
       </c>
       <c r="B38">
-        <v>-20.0193918691989</v>
+        <v>-19.975255398691953</v>
       </c>
       <c r="C38">
         <v>442.41419819725974</v>
@@ -1676,10 +1676,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>31.926272467090865</v>
+        <v>31.956247096576547</v>
       </c>
       <c r="B39">
-        <v>-21.352952297502934</v>
+        <v>-21.310863259096017</v>
       </c>
       <c r="C39">
         <v>442.41419819725974</v>
@@ -1687,10 +1687,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>33.346220497460642</v>
+        <v>33.375898724623951</v>
       </c>
       <c r="B40">
-        <v>-22.718005547247206</v>
+        <v>-22.678349418267409</v>
       </c>
       <c r="C40">
         <v>442.41419819725974</v>
@@ -1698,10 +1698,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>34.742927457693654</v>
+        <v>34.772191770539692</v>
       </c>
       <c r="B41">
-        <v>-24.120677869765309</v>
+        <v>-24.08385256407659</v>
       </c>
       <c r="C41">
         <v>442.41419819725974</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>34.742927457693654</v>
+        <v>34.772191770539692</v>
       </c>
       <c r="B42">
-        <v>-24.120677869765309</v>
+        <v>-24.08385256407659</v>
       </c>
       <c r="C42">
         <v>442.41419819725974</v>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>33.16855918273032</v>
+        <v>33.198941511280061</v>
       </c>
       <c r="B43">
-        <v>-23.005576381490286</v>
+        <v>-22.966354057300414</v>
       </c>
       <c r="C43">
         <v>442.41419819725974</v>
@@ -1731,10 +1731,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>31.601461763352081</v>
+        <v>31.63272367176609</v>
       </c>
       <c r="B44">
-        <v>-21.878705949540375</v>
+        <v>-21.837410018171507</v>
       </c>
       <c r="C44">
         <v>442.41419819725974</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>30.037900655265979</v>
+        <v>30.06982047141193</v>
       </c>
       <c r="B45">
-        <v>-20.746111480312198</v>
+        <v>-20.703071276918237</v>
       </c>
       <c r="C45">
         <v>442.41419819725974</v>
@@ -1753,10 +1753,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>28.474141314179036</v>
+        <v>28.506514129631739</v>
       </c>
       <c r="B46">
-        <v>-19.613837880202396</v>
+        <v>-19.56938866376899</v>
       </c>
       <c r="C46">
         <v>442.41419819725974</v>
@@ -1764,10 +1764,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>26.906956860109197</v>
+        <v>26.939592443703667</v>
       </c>
       <c r="B47">
-        <v>-18.487108326636221</v>
+        <v>-18.441590161623843</v>
       </c>
       <c r="C47">
         <v>442.41419819725974</v>
@@ -1775,10 +1775,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>25.335151070318087</v>
+        <v>25.367865522361846</v>
       </c>
       <c r="B48">
-        <v>-17.367859081153437</v>
+        <v>-17.321612364069658</v>
       </c>
       <c r="C48">
         <v>442.41419819725974</v>
@@ -1786,10 +1786,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>23.758035386378246</v>
+        <v>23.790649052204433</v>
       </c>
       <c r="B49">
-        <v>-16.257204676322445</v>
+        <v>-16.210569017365007</v>
       </c>
       <c r="C49">
         <v>442.41419819725974</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>22.1749212498622</v>
+        <v>22.207258719829547</v>
       </c>
       <c r="B50">
-        <v>-15.156259644711632</v>
+        <v>-15.109573867768461</v>
       </c>
       <c r="C50">
         <v>442.41419819725974</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>20.585326423212074</v>
+        <v>20.617215636971004</v>
       </c>
       <c r="B51">
-        <v>-14.065804558372003</v>
+        <v>-14.01940632426615</v>
       </c>
       <c r="C51">
         <v>442.41419819725974</v>
@@ -1819,10 +1819,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>18.989593952348311</v>
+        <v>19.020862615905294</v>
       </c>
       <c r="B52">
-        <v>-12.985284147285027</v>
+        <v>-12.939508446754491</v>
       </c>
       <c r="C52">
         <v>442.41419819725974</v>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>17.388273204060926</v>
+        <v>17.418747894044564</v>
       </c>
       <c r="B53">
-        <v>-11.913809180914774</v>
+        <v>-11.86898795785746</v>
       </c>
       <c r="C53">
         <v>442.41419819725974</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>15.781913545139931</v>
+        <v>15.811419708800965</v>
       </c>
       <c r="B54">
-        <v>-10.850490428725314</v>
+        <v>-10.806952580199013</v>
       </c>
       <c r="C54">
         <v>442.41419819725974</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>14.17093494466782</v>
+        <v>14.199297341410725</v>
       </c>
       <c r="B55">
-        <v>-9.79464810930451</v>
+        <v>-9.7527199175161758</v>
       </c>
       <c r="C55">
         <v>442.41419819725974</v>
@@ -1863,10 +1863,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>12.555239780896972</v>
+        <v>12.582284248406404</v>
       </c>
       <c r="B56">
-        <v>-8.7464402377354524</v>
+        <v>-8.7064470979981241</v>
       </c>
       <c r="C56">
         <v>442.41419819725974</v>
@@ -1874,10 +1874,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>10.934601034372216</v>
+        <v>10.960154930144613</v>
       </c>
       <c r="B57">
-        <v>-7.706234278224998</v>
+        <v>-7.6685011309470745</v>
       </c>
       <c r="C57">
         <v>442.41419819725974</v>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>9.30879168563841</v>
+        <v>9.3326838869820019</v>
       </c>
       <c r="B58">
-        <v>-6.6743976949800343</v>
+        <v>-6.6392490256652508</v>
       </c>
       <c r="C58">
         <v>442.41419819725974</v>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>7.6776120970201438</v>
+        <v>7.6996728238313592</v>
       </c>
       <c r="B59">
-        <v>-5.6512536307902286</v>
+        <v>-5.6190135149982252</v>
       </c>
       <c r="C59">
         <v>442.41419819725974</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>6.0409721579610665</v>
+        <v>6.0610322638302305</v>
       </c>
       <c r="B60">
-        <v>-4.6369479427765015</v>
+        <v>-4.60794022596503</v>
       </c>
       <c r="C60">
         <v>442.41419819725974</v>
@@ -1918,10 +1918,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>4.3988091396845821</v>
+        <v>4.4166999346723292</v>
       </c>
       <c r="B61">
-        <v>-3.6315821666425729</v>
+        <v>-3.6061305091280538</v>
       </c>
       <c r="C61">
         <v>442.41419819725974</v>
@@ -1929,10 +1929,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>2.7510603134141092</v>
+        <v>2.7666135640513914</v>
       </c>
       <c r="B62">
-        <v>-2.635257838092175</v>
+        <v>-2.6136857150496939</v>
       </c>
       <c r="C62">
         <v>442.41419819725974</v>
@@ -1940,10 +1940,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>1.0978342079050958</v>
+        <v>1.1108813878048158</v>
       </c>
       <c r="B63">
-        <v>-1.6477992874540923</v>
+        <v>-1.6304296857610583</v>
       </c>
       <c r="C63">
         <v>442.41419819725974</v>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-0.56007561795881422</v>
+        <v>-0.54970632565524369</v>
       </c>
       <c r="B64">
-        <v>-0.66792202355737818</v>
+        <v>-0.655076229168135</v>
       </c>
       <c r="C64">
         <v>442.41419819725974</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-2.2217043477619316</v>
+        <v>-2.2141887997729479</v>
       </c>
       <c r="B65">
-        <v>0.30593565014385021</v>
+        <v>0.31393835535436915</v>
       </c>
       <c r="C65">
         <v>442.41419819725974</v>
@@ -1973,10 +1973,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-3.8860871650885671</v>
+        <v>-3.8816052579924563</v>
       </c>
       <c r="B66">
-        <v>1.2753354301954754</v>
+        <v>1.2781777684317468</v>
       </c>
       <c r="C66">
         <v>442.41419819725974</v>
@@ -1984,10 +1984,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-5.5535098741311355</v>
+        <v>-5.5522406451481636</v>
       </c>
       <c r="B67">
-        <v>2.2398147006916851</v>
+        <v>2.237178251437705</v>
       </c>
       <c r="C67">
         <v>442.41419819725974</v>
@@ -1995,10 +1995,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-7.2292607615144471</v>
+        <v>-7.231362791635382</v>
       </c>
       <c r="B68">
-        <v>3.1908135959198707</v>
+        <v>3.1823662087395914</v>
       </c>
       <c r="C68">
         <v>442.41419819725974</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-8.9174381350571288</v>
+        <v>-8.9230543482405338</v>
       </c>
       <c r="B69">
-        <v>4.1216984049893357</v>
+        <v>4.10709696988957</v>
       </c>
       <c r="C69">
         <v>442.41419819725974</v>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-10.612377904920546</v>
+        <v>-10.621674361753479</v>
       </c>
       <c r="B70">
-        <v>5.0416372861037511</v>
+        <v>5.0205514021853572</v>
       </c>
       <c r="C70">
         <v>442.41419819725974</v>
@@ -2028,10 +2028,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-12.307904641443775</v>
+        <v>-12.321072629862652</v>
       </c>
       <c r="B71">
-        <v>5.9606260757911649</v>
+        <v>5.93273919533247</v>
       </c>
       <c r="C71">
         <v>442.41419819725974</v>
@@ -2039,10 +2039,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>-14.00555995333391</v>
+        <v>-14.022785557847232</v>
       </c>
       <c r="B72">
-        <v>6.8761694547827386</v>
+        <v>6.8411597909220374</v>
       </c>
       <c r="C72">
         <v>442.41419819725974</v>
@@ -2050,10 +2050,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>-15.707912888306016</v>
+        <v>-15.729372992608051</v>
       </c>
       <c r="B73">
-        <v>7.7841090434348477</v>
+        <v>7.7416469401263086</v>
       </c>
       <c r="C73">
         <v>442.41419819725974</v>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>-17.41392521173907</v>
+        <v>-17.439801939941816</v>
       </c>
       <c r="B74">
-        <v>8.6861253764016482</v>
+        <v>8.6358818805564521</v>
       </c>
       <c r="C74">
         <v>442.41419819725974</v>
@@ -2072,10 +2072,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>-19.121637568829602</v>
+        <v>-19.152122010055525</v>
       </c>
       <c r="B75">
-        <v>9.58538995613583</v>
+        <v>9.5270389462658489</v>
       </c>
       <c r="C75">
         <v>442.41419819725974</v>
@@ -2083,10 +2083,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>-20.82901340638039</v>
+        <v>-20.864306071901417</v>
       </c>
       <c r="B76">
-        <v>10.485199241986416</v>
+        <v>10.41841737063783</v>
       </c>
       <c r="C76">
         <v>442.41419819725974</v>
@@ -2094,10 +2094,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>-22.53416918054743</v>
+        <v>-22.574479475984319</v>
       </c>
       <c r="B77">
-        <v>11.388602025275137</v>
+        <v>11.313068217491527</v>
       </c>
       <c r="C77">
         <v>442.41419819725974</v>
@@ -2105,10 +2105,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>-24.235910583293208</v>
+        <v>-24.281454240274225</v>
       </c>
       <c r="B78">
-        <v>12.297531468318214</v>
+        <v>12.212924973059371</v>
       </c>
       <c r="C78">
         <v>442.41419819725974</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>-25.9321899726199</v>
+        <v>-25.98319250547781</v>
       </c>
       <c r="B79">
-        <v>13.215301979311052</v>
+        <v>13.121304331355027</v>
       </c>
       <c r="C79">
         <v>442.41419819725974</v>
@@ -2127,10 +2127,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>-27.619402577180438</v>
+        <v>-27.676105605485727</v>
       </c>
       <c r="B80">
-        <v>14.147748408148267</v>
+        <v>14.044046983853606</v>
       </c>
       <c r="C80">
         <v>442.41419819725974</v>
@@ -2138,10 +2138,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>-29.288667636880572</v>
+        <v>-29.35134991450316</v>
       </c>
       <c r="B81">
-        <v>15.109245564522615</v>
+        <v>14.99554627008982</v>
       </c>
       <c r="C81">
         <v>442.41419819725974</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>-30.779711131219795</v>
+        <v>-30.849288672567305</v>
       </c>
       <c r="B82">
-        <v>16.359220402764507</v>
+        <v>16.235617128153471</v>
       </c>
       <c r="C82">
         <v>442.41419819725974</v>
@@ -2170,10 +2170,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>-36.282262373534856</v>
+        <v>-36.366700994684784</v>
       </c>
       <c r="B1">
-        <v>14.235468441131765</v>
+        <v>14.026826961983453</v>
       </c>
       <c r="C1">
         <v>501.14832753435888</v>
@@ -2181,10 +2181,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>-34.049585835114726</v>
+        <v>-34.128477112089584</v>
       </c>
       <c r="B2">
-        <v>13.96974408710985</v>
+        <v>13.779635467629092</v>
       </c>
       <c r="C2">
         <v>501.14832753435888</v>
@@ -2192,10 +2192,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>-31.93753503834435</v>
+        <v>-32.010167089218854</v>
       </c>
       <c r="B3">
-        <v>13.423096843606141</v>
+        <v>13.250542563143567</v>
       </c>
       <c r="C3">
         <v>501.14832753435888</v>
@@ -2203,10 +2203,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>-29.845030739542462</v>
+        <v>-29.91149097038836</v>
       </c>
       <c r="B4">
-        <v>12.830928149925541</v>
+        <v>12.675292982123382</v>
       </c>
       <c r="C4">
         <v>501.14832753435888</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>-27.766455187438584</v>
+        <v>-27.826874885554592</v>
       </c>
       <c r="B5">
-        <v>12.206321075218241</v>
+        <v>12.066990145880858</v>
       </c>
       <c r="C5">
         <v>501.14832753435888</v>
@@ -2225,10 +2225,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>-25.699518427949627</v>
+        <v>-25.754046459225194</v>
       </c>
       <c r="B6">
-        <v>11.55460864798213</v>
+        <v>11.430976104593615</v>
       </c>
       <c r="C6">
         <v>501.14832753435888</v>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>-23.642913689071896</v>
+        <v>-23.69170875903124</v>
       </c>
       <c r="B7">
-        <v>10.878834183534128</v>
+        <v>10.770299772411267</v>
       </c>
       <c r="C7">
         <v>501.14832753435888</v>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>-21.595872934289538</v>
+        <v>-21.639099345637444</v>
       </c>
       <c r="B8">
-        <v>10.180786346833358</v>
+        <v>10.086753542008413</v>
       </c>
       <c r="C8">
         <v>501.14832753435888</v>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>-19.557195003529365</v>
+        <v>-19.595026129758665</v>
       </c>
       <c r="B9">
-        <v>9.4632624956732361</v>
+        <v>9.3831398554985572</v>
       </c>
       <c r="C9">
         <v>501.14832753435888</v>
@@ -2269,10 +2269,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-17.525582972298132</v>
+        <v>-17.558202038037479</v>
       </c>
       <c r="B10">
-        <v>8.7292830116995077</v>
+        <v>8.66248444981682</v>
       </c>
       <c r="C10">
         <v>501.14832753435888</v>
@@ -2280,10 +2280,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-15.499789981979674</v>
+        <v>-15.527389710777205</v>
       </c>
       <c r="B11">
-        <v>7.98175167913299</v>
+        <v>7.92769619174586</v>
       </c>
       <c r="C11">
         <v>501.14832753435888</v>
@@ -2291,10 +2291,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-13.479150666900502</v>
+        <v>-13.501928701306593</v>
       </c>
       <c r="B12">
-        <v>7.2222180548510408</v>
+        <v>7.18032770287896</v>
       </c>
       <c r="C12">
         <v>501.14832753435888</v>
@@ -2302,10 +2302,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-11.465275567280681</v>
+        <v>-11.483416501395366</v>
       </c>
       <c r="B13">
-        <v>6.4469313837821476</v>
+        <v>6.4166234942043152</v>
       </c>
       <c r="C13">
         <v>501.14832753435888</v>
@@ -2313,10 +2313,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-9.4591280750256</v>
+        <v>-9.472808598164324</v>
       </c>
       <c r="B14">
-        <v>5.6536480416877168</v>
+        <v>5.6343373435810165</v>
       </c>
       <c r="C14">
         <v>501.14832753435888</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-7.4568070828883322</v>
+        <v>-7.4662345216975927</v>
       </c>
       <c r="B15">
-        <v>4.8514532396097163</v>
+        <v>4.8425682069567939</v>
       </c>
       <c r="C15">
         <v>501.14832753435888</v>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-5.4547345141560752</v>
+        <v>-5.460144295868723</v>
       </c>
       <c r="B16">
-        <v>4.0486798892069995</v>
+        <v>4.0496616023416445</v>
       </c>
       <c r="C16">
         <v>501.14832753435888</v>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-3.4554889134047313</v>
+        <v>-3.4570958767456168</v>
       </c>
       <c r="B17">
-        <v>3.2393228693253553</v>
+        <v>3.2496041179059807</v>
       </c>
       <c r="C17">
         <v>501.14832753435888</v>
@@ -2357,10 +2357,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-1.4623999564938235</v>
+        <v>-1.4603924333536811</v>
       </c>
       <c r="B18">
-        <v>2.4156277641104209</v>
+        <v>2.4346304460506589</v>
       </c>
       <c r="C18">
         <v>501.14832753435888</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>0.52435477687142451</v>
+        <v>0.52978994564610282</v>
       </c>
       <c r="B19">
-        <v>1.5771810117202498</v>
+        <v>1.6043266259378637</v>
       </c>
       <c r="C19">
         <v>501.14832753435888</v>
@@ -2379,10 +2379,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>2.5053857310243814</v>
+        <v>2.5140569416838767</v>
       </c>
       <c r="B20">
-        <v>0.72540426381599077</v>
+        <v>0.76011653342010765</v>
       </c>
       <c r="C20">
         <v>501.14832753435888</v>
@@ -2390,10 +2390,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>4.4813033502983908</v>
+        <v>4.4930142361897571</v>
       </c>
       <c r="B21">
-        <v>-0.13828082794119756</v>
+        <v>-0.096575955650089224</v>
       </c>
       <c r="C21">
         <v>501.14832753435888</v>
@@ -2401,10 +2401,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>6.4526094119458621</v>
+        <v>6.4671596812517045</v>
       </c>
       <c r="B22">
-        <v>-1.0127056844927256</v>
+        <v>-0.9645804577494933</v>
       </c>
       <c r="C22">
         <v>501.14832753435888</v>
@@ -2412,10 +2412,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>8.41937102489534</v>
+        <v>8.4365598115889373</v>
       </c>
       <c r="B23">
-        <v>-1.897714017190238</v>
+        <v>-1.8437405586719771</v>
       </c>
       <c r="C23">
         <v>501.14832753435888</v>
@@ -2423,10 +2423,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>10.381546630994411</v>
+        <v>10.401173332578496</v>
       </c>
       <c r="B24">
-        <v>-2.79340260998794</v>
+        <v>-2.7341533365406887</v>
       </c>
       <c r="C24">
         <v>501.14832753435888</v>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>12.339094672090679</v>
+        <v>12.360958949597436</v>
       </c>
       <c r="B25">
-        <v>-3.699868246840043</v>
+        <v>-3.6359158694787865</v>
       </c>
       <c r="C25">
         <v>501.14832753435888</v>
@@ -2445,10 +2445,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>14.291955665728525</v>
+        <v>14.315857564161343</v>
       </c>
       <c r="B26">
-        <v>-4.6172494552538126</v>
+        <v>-4.5491670901011245</v>
       </c>
       <c r="C26">
         <v>501.14832753435888</v>
@@ -2456,10 +2456,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>16.239998432239545</v>
+        <v>16.265738862340037</v>
       </c>
       <c r="B27">
-        <v>-5.545851736948765</v>
+        <v>-5.4742133489894034</v>
       </c>
       <c r="C27">
         <v>501.14832753435888</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>18.183073867652119</v>
+        <v>18.210454726341879</v>
       </c>
       <c r="B28">
-        <v>-6.4860223371974666</v>
+        <v>-6.41140285121702</v>
       </c>
       <c r="C28">
         <v>501.14832753435888</v>
@@ -2478,10 +2478,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>20.121032867994646</v>
+        <v>20.149857038375245</v>
       </c>
       <c r="B29">
-        <v>-7.4381085012724926</v>
+        <v>-7.3610838018573821</v>
       </c>
       <c r="C29">
         <v>501.14832753435888</v>
@@ -2489,10 +2489,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>22.053807247630161</v>
+        <v>22.0838779369744</v>
       </c>
       <c r="B30">
-        <v>-8.4022690253469889</v>
+        <v>-8.3234157341198074</v>
       </c>
       <c r="C30">
         <v>501.14832753435888</v>
@@ -2500,10 +2500,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>23.981652494260285</v>
+        <v>24.012770585977194</v>
       </c>
       <c r="B31">
-        <v>-9.3779089091963534</v>
+        <v>-9.2978034937572467</v>
       </c>
       <c r="C31">
         <v>501.14832753435888</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>25.904905013921354</v>
+        <v>25.936868405547465</v>
       </c>
       <c r="B32">
-        <v>-10.36424470349659</v>
+        <v>-10.283463254658606</v>
       </c>
       <c r="C32">
         <v>501.14832753435888</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>27.823901212649623</v>
+        <v>27.856504815848957</v>
       </c>
       <c r="B33">
-        <v>-11.360492958923672</v>
+        <v>-11.27961119071275</v>
       </c>
       <c r="C33">
         <v>501.14832753435888</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>29.738846686335329</v>
+        <v>29.771883439445933</v>
       </c>
       <c r="B34">
-        <v>-12.366174867299852</v>
+        <v>-12.285768612566105</v>
       </c>
       <c r="C34">
         <v>501.14832753435888</v>
@@ -2544,10 +2544,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>31.649423790284459</v>
+        <v>31.682688708504518</v>
       </c>
       <c r="B35">
-        <v>-13.382030185032486</v>
+        <v>-13.302677377895272</v>
       </c>
       <c r="C35">
         <v>501.14832753435888</v>
@@ -2555,10 +2555,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>33.555184069656896</v>
+        <v>33.588475257591256</v>
       </c>
       <c r="B36">
-        <v>-14.409103309675178</v>
+        <v>-14.331384481134359</v>
       </c>
       <c r="C36">
         <v>501.14832753435888</v>
@@ -2566,10 +2566,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>35.455679069612543</v>
+        <v>35.488797721272732</v>
       </c>
       <c r="B37">
-        <v>-15.448438638781552</v>
+        <v>-15.372936916717508</v>
       </c>
       <c r="C37">
         <v>501.14832753435888</v>
@@ -2577,10 +2577,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>37.350139569217312</v>
+        <v>37.382892485956646</v>
       </c>
       <c r="B38">
-        <v>-16.501827595678819</v>
+        <v>-16.429129837840193</v>
       </c>
       <c r="C38">
         <v>501.14832753435888</v>
@@ -2588,10 +2588,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>39.236513283161173</v>
+        <v>39.268722945415185</v>
       </c>
       <c r="B39">
-        <v>-17.574049706788575</v>
+        <v>-17.504751032743282</v>
       </c>
       <c r="C39">
         <v>501.14832753435888</v>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>41.112427160040085</v>
+        <v>41.143934245261619</v>
       </c>
       <c r="B40">
-        <v>-18.670631524305975</v>
+        <v>-18.605336448428972</v>
       </c>
       <c r="C40">
         <v>501.14832753435888</v>
@@ -2610,10 +2610,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>42.975508148450018</v>
+        <v>43.006171531109267</v>
       </c>
       <c r="B41">
-        <v>-19.797099600426208</v>
+        <v>-19.736422031899476</v>
       </c>
       <c r="C41">
         <v>501.14832753435888</v>
@@ -2621,10 +2621,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>42.975508148450018</v>
+        <v>43.006171531109267</v>
       </c>
       <c r="B42">
-        <v>-19.797099600426208</v>
+        <v>-19.736422031899476</v>
       </c>
       <c r="C42">
         <v>501.14832753435888</v>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>41.000403580931646</v>
+        <v>41.032797172384669</v>
       </c>
       <c r="B43">
-        <v>-18.931521008613657</v>
+        <v>-18.8666048091827</v>
       </c>
       <c r="C43">
         <v>501.14832753435888</v>
@@ -2643,10 +2643,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>39.031705288687078</v>
+        <v>39.06553571297</v>
       </c>
       <c r="B44">
-        <v>-18.051022969789877</v>
+        <v>-17.98241697960351</v>
       </c>
       <c r="C44">
         <v>501.14832753435888</v>
@@ -2654,10 +2654,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>37.067045033363264</v>
+        <v>37.102038238014607</v>
       </c>
       <c r="B45">
-        <v>-17.161120827131381</v>
+        <v>-17.089380527110936</v>
       </c>
       <c r="C45">
         <v>501.14832753435888</v>
@@ -2665,10 +2665,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>35.104054576607162</v>
+        <v>35.13995583266793</v>
       </c>
       <c r="B46">
-        <v>-16.2673299238147</v>
+        <v>-16.193017435654014</v>
       </c>
       <c r="C46">
         <v>501.14832753435888</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>33.140686278986649</v>
+        <v>33.17725762344962</v>
       </c>
       <c r="B47">
-        <v>-15.374418966568742</v>
+        <v>-15.298102016552706</v>
       </c>
       <c r="C47">
         <v>501.14832753435888</v>
@@ -2687,10 +2687,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>31.176174896753395</v>
+        <v>31.213184902360432</v>
       </c>
       <c r="B48">
-        <v>-14.484170116331994</v>
+        <v>-14.406417890610774</v>
       </c>
       <c r="C48">
         <v>501.14832753435888</v>
@@ -2698,10 +2698,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>29.210075785079962</v>
+        <v>29.24729700277139</v>
       </c>
       <c r="B49">
-        <v>-13.59761889759532</v>
+        <v>-13.51900100600291</v>
       </c>
       <c r="C49">
         <v>501.14832753435888</v>
@@ -2709,10 +2709,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>27.241944299138982</v>
+        <v>27.279153258053558</v>
       </c>
       <c r="B50">
-        <v>-12.715800834849613</v>
+        <v>-12.636887310903829</v>
       </c>
       <c r="C50">
         <v>501.14832753435888</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>25.271466417891087</v>
+        <v>25.30844256903729</v>
       </c>
       <c r="B51">
-        <v>-11.839447245444903</v>
+        <v>-11.760808157759451</v>
       </c>
       <c r="C51">
         <v>501.14832753435888</v>
@@ -2731,10 +2731,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>23.298850615449183</v>
+        <v>23.33537210639026</v>
       </c>
       <c r="B52">
-        <v>-10.968072618167897</v>
+        <v>-10.890276516100615</v>
       </c>
       <c r="C52">
         <v>501.14832753435888</v>
@@ -2742,10 +2742,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>21.3244359897143</v>
+        <v>21.36027860823954</v>
       </c>
       <c r="B53">
-        <v>-10.100887234664482</v>
+        <v>-10.0245007597294</v>
       </c>
       <c r="C53">
         <v>501.14832753435888</v>
@@ -2753,10 +2753,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>19.348561638587363</v>
+        <v>19.383498812712091</v>
       </c>
       <c r="B54">
-        <v>-9.2371013765805063</v>
+        <v>-9.1626892624478558</v>
       </c>
       <c r="C54">
         <v>501.14832753435888</v>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>17.371485562007948</v>
+        <v>17.405288980091797</v>
       </c>
       <c r="B55">
-        <v>-8.3761141929905349</v>
+        <v>-8.30423959067957</v>
       </c>
       <c r="C55">
         <v>501.14832753435888</v>
@@ -2775,10 +2775,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>15.393141368069857</v>
+        <v>15.425583459289799</v>
       </c>
       <c r="B56">
-        <v>-7.5180803026838321</v>
+        <v>-7.4493060813341376</v>
       </c>
       <c r="C56">
         <v>501.14832753435888</v>
@@ -2786,10 +2786,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>13.413381566905441</v>
+        <v>13.444236121374033</v>
       </c>
       <c r="B57">
-        <v>-6.6633431918783321</v>
+        <v>-6.5982322639426609</v>
       </c>
       <c r="C57">
         <v>501.14832753435888</v>
@@ -2797,10 +2797,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>11.432058668647077</v>
+        <v>11.461100837412468</v>
       </c>
       <c r="B58">
-        <v>-5.8122463467919845</v>
+        <v>-5.7513616680362487</v>
       </c>
       <c r="C58">
         <v>501.14832753435888</v>
@@ -2808,10 +2808,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>9.4490429295162048</v>
+        <v>9.4760490627238134</v>
       </c>
       <c r="B59">
-        <v>-4.9650919251289594</v>
+        <v>-4.9089964849295713</v>
       </c>
       <c r="C59">
         <v>501.14832753435888</v>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>7.464275590090649</v>
+        <v>7.4890225896298439</v>
       </c>
       <c r="B60">
-        <v>-4.1220167705383854</v>
+        <v>-4.0712735530716007</v>
       </c>
       <c r="C60">
         <v>501.14832753435888</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>5.4777156370372984</v>
+        <v>5.4999807947030819</v>
       </c>
       <c r="B61">
-        <v>-3.2831163981556166</v>
+        <v>-3.2382883726948748</v>
       </c>
       <c r="C61">
         <v>501.14832753435888</v>
@@ -2841,10 +2841,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>3.4893220570230596</v>
+        <v>3.5088830545160574</v>
       </c>
       <c r="B62">
-        <v>-2.4484863231160126</v>
+        <v>-2.4101364440319339</v>
       </c>
       <c r="C62">
         <v>501.14832753435888</v>
@@ -2852,10 +2852,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>1.4991623186625478</v>
+        <v>1.5157963469041518</v>
       </c>
       <c r="B63">
-        <v>-1.6179694191055249</v>
+        <v>-1.5866603111699931</v>
       </c>
       <c r="C63">
         <v>501.14832753435888</v>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-0.49226218163881208</v>
+        <v>-0.47878194524590578</v>
       </c>
       <c r="B64">
-        <v>-0.79039799401245825</v>
+        <v>-0.7666906936149479</v>
       </c>
       <c r="C64">
         <v>501.14832753435888</v>
@@ -2874,10 +2874,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-2.4843415655278624</v>
+        <v>-2.4742468377845155</v>
       </c>
       <c r="B65">
-        <v>0.035648285724284287</v>
+        <v>0.051194645272625329</v>
       </c>
       <c r="C65">
         <v>501.14832753435888</v>
@@ -2885,10 +2885,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-4.4764659546514709</v>
+        <v>-4.4699933465621049</v>
       </c>
       <c r="B66">
-        <v>0.861589753665809</v>
+        <v>0.86841794213215973</v>
       </c>
       <c r="C66">
         <v>501.14832753435888</v>
@@ -2896,10 +2896,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-6.4688136435086552</v>
+        <v>-6.4661984408871538</v>
       </c>
       <c r="B67">
-        <v>1.6870111833010908</v>
+        <v>1.6845631658415887</v>
       </c>
       <c r="C67">
         <v>501.14832753435888</v>
@@ -2907,10 +2907,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-8.4647156180071121</v>
+        <v>-8.46616690390043</v>
       </c>
       <c r="B68">
-        <v>2.5041551078306119</v>
+        <v>2.4918612142328773</v>
       </c>
       <c r="C68">
         <v>501.14832753435888</v>
@@ -2918,10 +2918,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-10.466751947501457</v>
+        <v>-10.472458570421473</v>
       </c>
       <c r="B69">
-        <v>3.3070128550734132</v>
+        <v>3.2842942587832362</v>
       </c>
       <c r="C69">
         <v>501.14832753435888</v>
@@ -2929,10 +2929,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-12.471346343725219</v>
+        <v>-12.481525668152534</v>
       </c>
       <c r="B70">
-        <v>4.1039131716112314</v>
+        <v>4.0702026365967923</v>
       </c>
       <c r="C70">
         <v>501.14832753435888</v>
@@ -2940,10 +2940,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-14.474599650382103</v>
+        <v>-14.489500131383672</v>
       </c>
       <c r="B71">
-        <v>4.9039367249559591</v>
+        <v>4.8586796516553949</v>
       </c>
       <c r="C71">
         <v>501.14832753435888</v>
@@ -2951,10 +2951,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>-16.477477596677552</v>
+        <v>-16.497340327873474</v>
       </c>
       <c r="B72">
-        <v>5.7048344475774089</v>
+        <v>5.6474723098248507</v>
       </c>
       <c r="C72">
         <v>501.14832753435888</v>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>-18.481593245761971</v>
+        <v>-18.506646859017614</v>
       </c>
       <c r="B73">
-        <v>6.5028497088017945</v>
+        <v>6.4328178117795574</v>
       </c>
       <c r="C73">
         <v>501.14832753435888</v>
@@ -2973,10 +2973,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>-20.4862841110639</v>
+        <v>-20.516762827291672</v>
       </c>
       <c r="B74">
-        <v>7.2995253604230488</v>
+        <v>7.21626043554438</v>
       </c>
       <c r="C74">
         <v>501.14832753435888</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>-22.490306392715979</v>
+        <v>-22.52645464390454</v>
       </c>
       <c r="B75">
-        <v>8.0977580632027539</v>
+        <v>8.00070018300844</v>
       </c>
       <c r="C75">
         <v>501.14832753435888</v>
@@ -2995,10 +2995,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>-24.492366587389181</v>
+        <v>-24.534439453918559</v>
       </c>
       <c r="B76">
-        <v>8.9005602313053842</v>
+        <v>8.7891528741674474</v>
       </c>
       <c r="C76">
         <v>501.14832753435888</v>
@@ -3006,10 +3006,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>-26.491267141201106</v>
+        <v>-26.539529615049727</v>
       </c>
       <c r="B77">
-        <v>9.7107208241383951</v>
+        <v>9.5844104968313335</v>
       </c>
       <c r="C77">
         <v>501.14832753435888</v>
@@ -3017,10 +3017,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>-28.486244001517537</v>
+        <v>-28.540967601775218</v>
       </c>
       <c r="B78">
-        <v>10.530019228678262</v>
+        <v>10.388253891960313</v>
       </c>
       <c r="C78">
         <v>501.14832753435888</v>
@@ -3028,10 +3028,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>-30.475994551032947</v>
+        <v>-30.537461606734947</v>
       </c>
       <c r="B79">
-        <v>11.361489084447941</v>
+        <v>11.203719925495161</v>
       </c>
       <c r="C79">
         <v>501.14832753435888</v>
@@ -3039,10 +3039,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>-32.458233329380192</v>
+        <v>-32.526744798825263</v>
       </c>
       <c r="B80">
-        <v>12.210452954619772</v>
+        <v>12.036137613498919</v>
       </c>
       <c r="C80">
         <v>501.14832753435888</v>
@@ -3050,10 +3050,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>-34.427347340376024</v>
+        <v>-34.503249175921688</v>
       </c>
       <c r="B81">
-        <v>13.089982834315817</v>
+        <v>12.898596582592777</v>
       </c>
       <c r="C81">
         <v>501.14832753435888</v>
@@ -3061,10 +3061,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>-36.282262373534856</v>
+        <v>-36.366700994684784</v>
       </c>
       <c r="B82">
-        <v>14.235468441131765</v>
+        <v>14.026826961983453</v>
       </c>
       <c r="C82">
         <v>501.14832753435888</v>
